--- a/AI Planning/Job Scheduling/Job To Machine/problemset/solution/sjf/reparacion-150j-10m-30_300tr-constantd-450c_sjf.xlsx
+++ b/AI Planning/Job Scheduling/Job To Machine/problemset/solution/sjf/reparacion-150j-10m-30_300tr-constantd-450c_sjf.xlsx
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 0354</t>
+          <t>AMD Ryzen 0 0778X</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -479,12 +479,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dell e040</t>
+          <t>NVIDIA RTX 9708</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -500,12 +500,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 021</t>
+          <t>MacBook Air 51</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -521,12 +521,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HP Gen 9 QL-T992</t>
+          <t>HP Gen 5 Rc-a957</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -542,12 +542,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Intel Core i3-994K</t>
+          <t>MacBook Pro 42</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -563,12 +563,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MacBook Pro 57</t>
+          <t>NVIDIA RTX 9390</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -584,12 +584,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dell Y125</t>
+          <t>Intel Core i4-597K</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -605,12 +605,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 3279</t>
+          <t>HP Gen 7 oE-J659</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -626,12 +626,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 2849</t>
+          <t>HP Gen 0 gg-f701</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -647,12 +647,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MacBook Air 74</t>
+          <t>MacBook Pro 99</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -668,12 +668,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 0990</t>
+          <t>NVIDIA RTX 7566</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -689,12 +689,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dell h264</t>
+          <t>NVIDIA RTX 9187</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -710,12 +710,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HP Gen 9 LW-B375</t>
+          <t>NVIDIA RTX 3287</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -731,12 +731,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 613</t>
+          <t>NVIDIA RTX 5405</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -752,12 +752,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MacBook Pro 64</t>
+          <t>AMD Ryzen 5 4072X</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Paula Marcela</t>
+          <t>Julián Buitrago</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -773,12 +773,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MacBook Air 40</t>
+          <t>Dell c991</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -794,12 +794,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dell Q081</t>
+          <t>Dell T136</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -815,12 +815,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMD Ryzen 6 3485X</t>
+          <t>Intel Core i5-942K</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -836,12 +836,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HP Gen 8 Cv-G617</t>
+          <t>NVIDIA GeForce 157</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -857,12 +857,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MacBook Pro 03</t>
+          <t>NVIDIA RTX 7130</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -878,12 +878,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HP Gen 6 Be-J242</t>
+          <t>NVIDIA RTX 0174</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -899,12 +899,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MacBook Air 61</t>
+          <t>Intel Core i4-834K</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -920,12 +920,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMD Ryzen 1 0728X</t>
+          <t>AMD Ryzen 8 9976X</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -941,12 +941,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dell t534</t>
+          <t>AMD Ryzen 4 9742X</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -962,12 +962,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Intel Core i4-078K</t>
+          <t>AMD Ryzen 3 2806X</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -983,12 +983,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 873</t>
+          <t>Dell s558</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1004,12 +1004,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AMD Ryzen 0 5815X</t>
+          <t>MacBook Pro 05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1025,12 +1025,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 041</t>
+          <t>Dell U159</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1046,12 +1046,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MacBook Pro 82</t>
+          <t>MacBook Air 97</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1067,12 +1067,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MacBook Air 70</t>
+          <t>MacBook Pro 63</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Piedad Bustamante</t>
+          <t>Dary María</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1088,12 +1088,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HP Gen 5 KK-G127</t>
+          <t>AMD Ryzen 0 7365X</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1109,12 +1109,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MacBook Air 68</t>
+          <t>NVIDIA RTX 5504</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1130,12 +1130,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 481</t>
+          <t>MacBook Pro 45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1151,12 +1151,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Intel Core i7-167K</t>
+          <t>AMD Ryzen 9 4419X</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1172,12 +1172,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dell A698</t>
+          <t>NVIDIA GeForce 194</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1193,12 +1193,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MacBook Air 86</t>
+          <t>Intel Core i3-293K</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1214,12 +1214,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MacBook Pro 41</t>
+          <t>MacBook Air 13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1235,12 +1235,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Intel Core i5-291K</t>
+          <t>Dell l752</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1256,12 +1256,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dell X509</t>
+          <t>MacBook Air 60</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1277,12 +1277,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 0833X</t>
+          <t>MacBook Air 85</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1298,12 +1298,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 546</t>
+          <t>MacBook Pro 55</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1319,12 +1319,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dell f563</t>
+          <t>Dell k750</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1340,12 +1340,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 3150X</t>
+          <t>MacBook Pro 90</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1361,12 +1361,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Intel Core i6-231K</t>
+          <t>NVIDIA GeForce 340</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1382,12 +1382,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MacBook Pro 46</t>
+          <t>Intel Core i2-053K</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Luis Carrillo</t>
+          <t>Marcela Ruby</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1403,12 +1403,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HP Gen 7 fB-B116</t>
+          <t>Intel Core i6-424K</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1424,12 +1424,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HP Gen 3 zK-a500</t>
+          <t>NVIDIA RTX 8519</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1445,12 +1445,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 441</t>
+          <t>MacBook Air 68</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1466,12 +1466,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dell s223</t>
+          <t>Dell q200</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1487,12 +1487,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Intel Core i2-090K</t>
+          <t>NVIDIA GeForce 336</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1508,12 +1508,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Intel Core i9-792K</t>
+          <t>MacBook Air 19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1529,12 +1529,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 9177</t>
+          <t>NVIDIA GeForce 994</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1550,12 +1550,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HP Gen 5 rE-g093</t>
+          <t>MacBook Air 14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1571,12 +1571,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Intel Core i5-903K</t>
+          <t>AMD Ryzen 4 3515X</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1592,12 +1592,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AMD Ryzen 2 4601X</t>
+          <t>HP Gen 6 hS-F815</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1613,12 +1613,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 7450</t>
+          <t>NVIDIA RTX 2182</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1634,12 +1634,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MacBook Pro 61</t>
+          <t>NVIDIA RTX 2742</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1655,12 +1655,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Intel Core i4-443K</t>
+          <t>Dell F879</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1676,12 +1676,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AMD Ryzen 3 3808X</t>
+          <t>Dell m564</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1697,12 +1697,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MacBook Pro 96</t>
+          <t>Dell N530</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mario Camilo</t>
+          <t>Carlos Lara</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1718,12 +1718,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AMD Ryzen 8 2586X</t>
+          <t>NVIDIA RTX 2166</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1739,12 +1739,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 9981</t>
+          <t>Intel Core i4-462K</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1760,12 +1760,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 6965</t>
+          <t>Dell k020</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1781,12 +1781,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 9634</t>
+          <t>Dell t458</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1802,12 +1802,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Intel Core i0-639K</t>
+          <t>AMD Ryzen 1 9911X</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1823,12 +1823,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dell V851</t>
+          <t>HP Gen 5 Sb-z136</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1844,12 +1844,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 514</t>
+          <t>Dell I389</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1865,12 +1865,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 9213</t>
+          <t>NVIDIA RTX 5631</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1886,12 +1886,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Intel Core i8-402K</t>
+          <t>MacBook Air 31</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1907,12 +1907,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Dell E637</t>
+          <t>AMD Ryzen 0 8696X</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1928,12 +1928,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 7404</t>
+          <t>NVIDIA RTX 5514</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1949,12 +1949,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 4689</t>
+          <t>NVIDIA GeForce 219</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1970,12 +1970,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Intel Core i0-755K</t>
+          <t>NVIDIA GeForce 936</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1991,12 +1991,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 652</t>
+          <t>NVIDIA RTX 7674</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2012,12 +2012,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 066</t>
+          <t>AMD Ryzen 7 1606X</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Eliecer Samuel</t>
+          <t>Miguel Julio</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2033,12 +2033,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 790</t>
+          <t>MacBook Air 79</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2054,12 +2054,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MacBook Air 33</t>
+          <t>NVIDIA GeForce 195</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -2075,12 +2075,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Intel Core i8-733K</t>
+          <t>Intel Core i4-432K</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2096,12 +2096,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MacBook Air 27</t>
+          <t>Dell u766</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2117,12 +2117,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Dell c469</t>
+          <t>Intel Core i9-026K</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2138,12 +2138,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HP Gen 8 re-i834</t>
+          <t>Dell y520</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2159,12 +2159,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 953</t>
+          <t>MacBook Pro 91</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2180,12 +2180,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Intel Core i0-429K</t>
+          <t>Dell A066</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2201,12 +2201,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 656</t>
+          <t>AMD Ryzen 7 2010X</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2222,12 +2222,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 967</t>
+          <t>AMD Ryzen 8 1539X</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2243,12 +2243,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MacBook Air 54</t>
+          <t>NVIDIA RTX 7722</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2264,12 +2264,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AMD Ryzen 0 0539X</t>
+          <t>MacBook Air 63</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2285,12 +2285,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MacBook Pro 80</t>
+          <t>HP Gen 3 Pp-u530</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2306,12 +2306,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HP Gen 5 pL-R410</t>
+          <t>NVIDIA RTX 6899</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2327,12 +2327,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MacBook Air 23</t>
+          <t>NVIDIA RTX 7544</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Fredy Ramírez</t>
+          <t>Jesús Acevedo</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -2348,12 +2348,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 036</t>
+          <t>Intel Core i0-923K</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2369,12 +2369,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AMD Ryzen 3 7615X</t>
+          <t>NVIDIA RTX 7358</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2390,12 +2390,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Dell x966</t>
+          <t>MacBook Air 50</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2411,12 +2411,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HP Gen 8 Py-w779</t>
+          <t>Intel Core i3-066K</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2432,12 +2432,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 3337</t>
+          <t>Intel Core i4-998K</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2453,12 +2453,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 633</t>
+          <t>Dell z621</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -2474,12 +2474,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MacBook Air 32</t>
+          <t>MacBook Air 73</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2495,12 +2495,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HP Gen 3 VQ-T653</t>
+          <t>HP Gen 8 CT-j750</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2516,12 +2516,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 298</t>
+          <t>NVIDIA RTX 9364</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2537,12 +2537,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AMD Ryzen 4 6821X</t>
+          <t>AMD Ryzen 5 6913X</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2558,12 +2558,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 8750</t>
+          <t>HP Gen 6 eq-c752</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2579,12 +2579,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 825</t>
+          <t>Dell Q304</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2600,12 +2600,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Intel Core i4-970K</t>
+          <t>MacBook Pro 64</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2621,12 +2621,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AMD Ryzen 9 4104X</t>
+          <t>NVIDIA RTX 5667</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2642,12 +2642,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MacBook Pro 85</t>
+          <t>NVIDIA GeForce 160</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Elena Blanca</t>
+          <t>José Hernán</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2663,12 +2663,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Dell m967</t>
+          <t>AMD Ryzen 1 8551X</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2684,12 +2684,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Intel Core i9-994K</t>
+          <t>NVIDIA GeForce 398</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2705,12 +2705,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 0658</t>
+          <t>MacBook Pro 85</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2726,12 +2726,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AMD Ryzen 0 0533X</t>
+          <t>Intel Core i5-535K</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2747,12 +2747,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Intel Core i2-208K</t>
+          <t>NVIDIA GeForce 843</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2768,12 +2768,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HP Gen 7 Ay-v103</t>
+          <t>MacBook Pro 93</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2789,12 +2789,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 6690</t>
+          <t>Dell v642</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2810,12 +2810,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MacBook Air 35</t>
+          <t>HP Gen 4 Ih-D431</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2831,12 +2831,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AMD Ryzen 8 6659X</t>
+          <t>NVIDIA RTX 7556</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2852,12 +2852,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MacBook Air 42</t>
+          <t>MacBook Pro 78</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2873,12 +2873,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>HP Gen 9 Ii-M771</t>
+          <t>NVIDIA RTX 8179</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2894,12 +2894,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 420</t>
+          <t>Dell e473</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2915,12 +2915,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MacBook Air 83</t>
+          <t>AMD Ryzen 2 6921X</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2936,12 +2936,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MacBook Air 80</t>
+          <t>MacBook Air 17</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2957,12 +2957,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Intel Core i8-550K</t>
+          <t>MacBook Pro 69</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Eduardo Antonio</t>
+          <t>Hernán García</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2978,12 +2978,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 311</t>
+          <t>MacBook Pro 47</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2999,12 +2999,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Dell g409</t>
+          <t>Dell J283</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -3020,12 +3020,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 422</t>
+          <t>Dell W171</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3041,12 +3041,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>HP Gen 4 ZE-A978</t>
+          <t>NVIDIA RTX 4516</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3062,12 +3062,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MacBook Air 79</t>
+          <t>NVIDIA RTX 2078</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -3083,12 +3083,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 3660</t>
+          <t>AMD Ryzen 0 0373X</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -3104,12 +3104,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>HP Gen 4 mj-M668</t>
+          <t>HP Gen 6 Fp-l683</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3125,12 +3125,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 269</t>
+          <t>NVIDIA RTX 6873</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -3146,12 +3146,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>HP Gen 6 Xx-R727</t>
+          <t>HP Gen 7 Ka-c269</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3167,12 +3167,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 7352</t>
+          <t>HP Gen 9 NU-w913</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3188,12 +3188,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Intel Core i4-511K</t>
+          <t>NVIDIA GeForce 199</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3209,12 +3209,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>HP Gen 9 cl-r030</t>
+          <t>MacBook Pro 36</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -3230,12 +3230,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Intel Core i3-281K</t>
+          <t>NVIDIA GeForce 535</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -3251,12 +3251,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MacBook Air 82</t>
+          <t>AMD Ryzen 1 4898X</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -3272,12 +3272,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Dell I207</t>
+          <t>AMD Ryzen 1 9495X</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Patricia Adriana</t>
+          <t>Jesús Pablo</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3293,12 +3293,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MacBook Pro 94</t>
+          <t>Dell r508</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -3314,12 +3314,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 7978</t>
+          <t>NVIDIA GeForce 090</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -3335,12 +3335,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 407</t>
+          <t>MacBook Pro 02</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -3356,12 +3356,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 8574</t>
+          <t>Intel Core i3-651K</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -3377,12 +3377,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 8176</t>
+          <t>AMD Ryzen 7 5909X</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -3398,12 +3398,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MacBook Pro 69</t>
+          <t>MacBook Air 82</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -3419,12 +3419,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Dell e319</t>
+          <t>NVIDIA GeForce 518</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -3440,12 +3440,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Intel Core i9-652K</t>
+          <t>MacBook Air 93</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -3461,12 +3461,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 6636</t>
+          <t>HP Gen 8 Jc-b515</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -3482,12 +3482,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Intel Core i1-394K</t>
+          <t>MacBook Pro 32</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -3503,12 +3503,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MacBook Pro 18</t>
+          <t>NVIDIA GeForce 433</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -3524,12 +3524,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Intel Core i3-747K</t>
+          <t>NVIDIA RTX 4277</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -3545,12 +3545,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MacBook Pro 72</t>
+          <t>NVIDIA GeForce 033</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -3566,12 +3566,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 307</t>
+          <t>Intel Core i5-653K</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -3587,12 +3587,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MacBook Air 41</t>
+          <t>HP Gen 3 dq-U817</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Antonio Emiro</t>
+          <t>Elvia Beatriz</t>
         </is>
       </c>
       <c r="C151" t="n">

--- a/AI Planning/Job Scheduling/Job To Machine/problemset/solution/sjf/reparacion-150j-10m-30_300tr-constantd-450c_sjf.xlsx
+++ b/AI Planning/Job Scheduling/Job To Machine/problemset/solution/sjf/reparacion-150j-10m-30_300tr-constantd-450c_sjf.xlsx
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AMD Ryzen 0 0778X</t>
+          <t>NVIDIA GeForce 053</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -479,12 +479,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 9708</t>
+          <t>AMD Ryzen 6 4584X</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -500,12 +500,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MacBook Air 51</t>
+          <t>MacBook Pro 64</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -521,12 +521,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HP Gen 5 Rc-a957</t>
+          <t>Intel Core i1-021K</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -542,12 +542,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MacBook Pro 42</t>
+          <t>AMD Ryzen 6 5237X</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -563,12 +563,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 9390</t>
+          <t>HP Gen 9 em-Q132</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -584,12 +584,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Intel Core i4-597K</t>
+          <t>MacBook Pro 92</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -605,12 +605,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HP Gen 7 oE-J659</t>
+          <t>Intel Core i8-242K</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -626,12 +626,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HP Gen 0 gg-f701</t>
+          <t>MacBook Pro 67</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -647,12 +647,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MacBook Pro 99</t>
+          <t>MacBook Pro 70</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -668,12 +668,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 7566</t>
+          <t>HP Gen 1 qf-D314</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -689,12 +689,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 9187</t>
+          <t>AMD Ryzen 4 7197X</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -710,12 +710,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 3287</t>
+          <t>NVIDIA GeForce 296</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -731,12 +731,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 5405</t>
+          <t>NVIDIA GeForce 869</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -752,12 +752,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 4072X</t>
+          <t>MacBook Pro 53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Julián Buitrago</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -773,12 +773,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dell c991</t>
+          <t>NVIDIA RTX 1657</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -794,12 +794,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dell T136</t>
+          <t>Intel Core i8-593K</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -815,12 +815,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Intel Core i5-942K</t>
+          <t>HP Gen 3 El-r136</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -836,12 +836,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 157</t>
+          <t>MacBook Pro 65</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -857,12 +857,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 7130</t>
+          <t>HP Gen 9 eX-i441</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -878,12 +878,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 0174</t>
+          <t>NVIDIA GeForce 037</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -899,12 +899,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intel Core i4-834K</t>
+          <t>AMD Ryzen 7 9506X</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -920,12 +920,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMD Ryzen 8 9976X</t>
+          <t>NVIDIA GeForce 697</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -941,12 +941,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AMD Ryzen 4 9742X</t>
+          <t>NVIDIA GeForce 165</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -962,12 +962,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMD Ryzen 3 2806X</t>
+          <t>Intel Core i8-675K</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -983,12 +983,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dell s558</t>
+          <t>AMD Ryzen 3 7641X</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1004,12 +1004,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MacBook Pro 05</t>
+          <t>HP Gen 6 bR-u704</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1025,12 +1025,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dell U159</t>
+          <t>MacBook Pro 13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1046,12 +1046,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MacBook Air 97</t>
+          <t>NVIDIA RTX 1505</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1067,12 +1067,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MacBook Pro 63</t>
+          <t>Dell V834</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dary María</t>
+          <t>Alexis Hernández</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1088,12 +1088,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AMD Ryzen 0 7365X</t>
+          <t>HP Gen 0 Bf-V648</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1109,12 +1109,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 5504</t>
+          <t>MacBook Pro 87</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1130,12 +1130,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MacBook Pro 45</t>
+          <t>Intel Core i3-016K</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1151,12 +1151,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AMD Ryzen 9 4419X</t>
+          <t>NVIDIA RTX 1268</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1172,12 +1172,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 194</t>
+          <t>AMD Ryzen 8 2680X</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1193,12 +1193,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Intel Core i3-293K</t>
+          <t>AMD Ryzen 9 8375X</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1214,12 +1214,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MacBook Air 13</t>
+          <t>NVIDIA RTX 8599</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1235,12 +1235,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dell l752</t>
+          <t>AMD Ryzen 2 6430X</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1256,12 +1256,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MacBook Air 60</t>
+          <t>HP Gen 8 Ye-R091</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1277,12 +1277,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MacBook Air 85</t>
+          <t>MacBook Air 05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1298,12 +1298,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MacBook Pro 55</t>
+          <t>AMD Ryzen 5 8571X</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1319,12 +1319,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dell k750</t>
+          <t>Dell o249</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1340,12 +1340,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MacBook Pro 90</t>
+          <t>Dell u880</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1361,12 +1361,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 340</t>
+          <t>Intel Core i2-757K</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1382,12 +1382,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Intel Core i2-053K</t>
+          <t>NVIDIA RTX 2988</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Marcela Ruby</t>
+          <t>María Moreno</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1403,12 +1403,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Intel Core i6-424K</t>
+          <t>MacBook Pro 90</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1424,12 +1424,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 8519</t>
+          <t>NVIDIA GeForce 801</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1445,12 +1445,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MacBook Air 68</t>
+          <t>AMD Ryzen 8 5049X</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1466,12 +1466,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dell q200</t>
+          <t>NVIDIA GeForce 390</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1487,12 +1487,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 336</t>
+          <t>NVIDIA RTX 4188</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1508,12 +1508,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MacBook Air 19</t>
+          <t>NVIDIA GeForce 299</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1529,12 +1529,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 994</t>
+          <t>NVIDIA RTX 4222</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1550,12 +1550,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MacBook Air 14</t>
+          <t>MacBook Pro 33</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1571,12 +1571,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AMD Ryzen 4 3515X</t>
+          <t>NVIDIA RTX 1659</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1592,12 +1592,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HP Gen 6 hS-F815</t>
+          <t>MacBook Air 15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1613,12 +1613,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 2182</t>
+          <t>HP Gen 9 lW-D367</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1634,12 +1634,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 2742</t>
+          <t>NVIDIA RTX 5239</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1655,12 +1655,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dell F879</t>
+          <t>NVIDIA GeForce 828</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1676,12 +1676,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Dell m564</t>
+          <t>Intel Core i6-527K</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1697,12 +1697,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dell N530</t>
+          <t>Dell q988</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Carlos Lara</t>
+          <t>Jackeline María</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1718,12 +1718,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 2166</t>
+          <t>MacBook Air 34</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1739,12 +1739,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Intel Core i4-462K</t>
+          <t>Dell u084</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1760,12 +1760,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dell k020</t>
+          <t>AMD Ryzen 8 5728X</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1781,12 +1781,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dell t458</t>
+          <t>MacBook Air 87</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1802,12 +1802,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AMD Ryzen 1 9911X</t>
+          <t>MacBook Air 61</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1823,12 +1823,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HP Gen 5 Sb-z136</t>
+          <t>NVIDIA GeForce 127</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1844,12 +1844,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Dell I389</t>
+          <t>HP Gen 7 rD-B301</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1865,12 +1865,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 5631</t>
+          <t>Dell E294</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1886,12 +1886,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MacBook Air 31</t>
+          <t>Intel Core i5-728K</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1907,12 +1907,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AMD Ryzen 0 8696X</t>
+          <t>NVIDIA GeForce 337</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1928,12 +1928,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 5514</t>
+          <t>HP Gen 7 vv-J469</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1949,12 +1949,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 219</t>
+          <t>Intel Core i7-317K</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1970,12 +1970,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 936</t>
+          <t>Dell k271</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1991,12 +1991,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 7674</t>
+          <t>MacBook Air 52</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2012,12 +2012,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 1606X</t>
+          <t>MacBook Air 69</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Miguel Julio</t>
+          <t>Didier García</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2033,12 +2033,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MacBook Air 79</t>
+          <t>MacBook Pro 39</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2054,12 +2054,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 195</t>
+          <t>NVIDIA RTX 4806</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -2075,12 +2075,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Intel Core i4-432K</t>
+          <t>MacBook Pro 42</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2096,12 +2096,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Dell u766</t>
+          <t>Intel Core i2-623K</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2117,12 +2117,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Intel Core i9-026K</t>
+          <t>NVIDIA GeForce 717</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2138,12 +2138,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Dell y520</t>
+          <t>NVIDIA RTX 1363</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2159,12 +2159,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MacBook Pro 91</t>
+          <t>HP Gen 8 uC-D612</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2180,12 +2180,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Dell A066</t>
+          <t>MacBook Air 37</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2201,12 +2201,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 2010X</t>
+          <t>Dell c259</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2222,12 +2222,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AMD Ryzen 8 1539X</t>
+          <t>AMD Ryzen 7 0866X</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2243,12 +2243,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 7722</t>
+          <t>Intel Core i0-247K</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2264,12 +2264,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MacBook Air 63</t>
+          <t>NVIDIA RTX 6822</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2285,12 +2285,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HP Gen 3 Pp-u530</t>
+          <t>HP Gen 8 MU-n207</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2306,12 +2306,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 6899</t>
+          <t>MacBook Air 28</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2327,12 +2327,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 7544</t>
+          <t>Intel Core i3-501K</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jesús Acevedo</t>
+          <t>Adolfo Martínez</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -2348,12 +2348,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Intel Core i0-923K</t>
+          <t>AMD Ryzen 4 3520X</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2369,12 +2369,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 7358</t>
+          <t>Dell J528</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2390,12 +2390,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MacBook Air 50</t>
+          <t>HP Gen 6 tr-t270</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2411,12 +2411,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Intel Core i3-066K</t>
+          <t>Intel Core i3-060K</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2432,12 +2432,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Intel Core i4-998K</t>
+          <t>MacBook Pro 73</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2453,12 +2453,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Dell z621</t>
+          <t>NVIDIA GeForce 129</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -2474,12 +2474,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MacBook Air 73</t>
+          <t>MacBook Pro 72</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2495,12 +2495,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>HP Gen 8 CT-j750</t>
+          <t>NVIDIA GeForce 195</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2516,12 +2516,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 9364</t>
+          <t>NVIDIA GeForce 152</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2537,12 +2537,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AMD Ryzen 5 6913X</t>
+          <t>Dell t003</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2558,12 +2558,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HP Gen 6 eq-c752</t>
+          <t>AMD Ryzen 9 7462X</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2579,12 +2579,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Dell Q304</t>
+          <t>MacBook Pro 62</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2600,12 +2600,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MacBook Pro 64</t>
+          <t>MacBook Pro 43</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2621,12 +2621,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 5667</t>
+          <t>HP Gen 9 It-l256</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2642,12 +2642,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 160</t>
+          <t>AMD Ryzen 0 0641X</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>José Hernán</t>
+          <t>Tatiana Jessica</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2663,12 +2663,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AMD Ryzen 1 8551X</t>
+          <t>MacBook Air 72</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2684,12 +2684,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 398</t>
+          <t>NVIDIA GeForce 810</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2705,12 +2705,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MacBook Pro 85</t>
+          <t>Intel Core i5-093K</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2726,12 +2726,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Intel Core i5-535K</t>
+          <t>AMD Ryzen 4 5287X</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2747,12 +2747,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 843</t>
+          <t>Dell w331</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2768,12 +2768,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MacBook Pro 93</t>
+          <t>Dell b170</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2789,12 +2789,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Dell v642</t>
+          <t>Intel Core i4-604K</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2810,12 +2810,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>HP Gen 4 Ih-D431</t>
+          <t>NVIDIA GeForce 326</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2831,12 +2831,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 7556</t>
+          <t>MacBook Air 09</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2852,12 +2852,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MacBook Pro 78</t>
+          <t>AMD Ryzen 5 9855X</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2873,12 +2873,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 8179</t>
+          <t>AMD Ryzen 9 7632X</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2894,12 +2894,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Dell e473</t>
+          <t>HP Gen 5 AL-B777</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2915,12 +2915,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AMD Ryzen 2 6921X</t>
+          <t>AMD Ryzen 8 9276X</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2936,12 +2936,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MacBook Air 17</t>
+          <t>Intel Core i7-135K</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2957,12 +2957,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MacBook Pro 69</t>
+          <t>AMD Ryzen 7 9843X</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Hernán García</t>
+          <t>Felipe Rodríguez</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2978,12 +2978,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MacBook Pro 47</t>
+          <t>Dell T804</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2999,12 +2999,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Dell J283</t>
+          <t>AMD Ryzen 8 9457X</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -3020,12 +3020,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Dell W171</t>
+          <t>MacBook Air 26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -3041,12 +3041,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 4516</t>
+          <t>NVIDIA RTX 7570</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -3062,12 +3062,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 2078</t>
+          <t>AMD Ryzen 2 1670X</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -3083,12 +3083,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AMD Ryzen 0 0373X</t>
+          <t>NVIDIA GeForce 601</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -3104,12 +3104,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>HP Gen 6 Fp-l683</t>
+          <t>NVIDIA RTX 3617</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3125,12 +3125,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 6873</t>
+          <t>Intel Core i6-579K</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -3146,12 +3146,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>HP Gen 7 Ka-c269</t>
+          <t>AMD Ryzen 7 1963X</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3167,12 +3167,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HP Gen 9 NU-w913</t>
+          <t>NVIDIA GeForce 855</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3188,12 +3188,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 199</t>
+          <t>HP Gen 9 WK-T794</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3209,12 +3209,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MacBook Pro 36</t>
+          <t>NVIDIA GeForce 250</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -3230,12 +3230,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 535</t>
+          <t>NVIDIA GeForce 876</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -3251,12 +3251,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AMD Ryzen 1 4898X</t>
+          <t>HP Gen 7 yK-S030</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -3272,12 +3272,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AMD Ryzen 1 9495X</t>
+          <t>NVIDIA GeForce 302</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Jesús Pablo</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3293,12 +3293,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Dell r508</t>
+          <t>NVIDIA GeForce 740</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -3314,12 +3314,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 090</t>
+          <t>NVIDIA RTX 3765</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -3335,12 +3335,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MacBook Pro 02</t>
+          <t>MacBook Pro 45</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -3356,12 +3356,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Intel Core i3-651K</t>
+          <t>HP Gen 8 hH-S822</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -3377,12 +3377,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AMD Ryzen 7 5909X</t>
+          <t>NVIDIA GeForce 850</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -3398,12 +3398,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MacBook Air 82</t>
+          <t>Dell j196</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -3419,12 +3419,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 518</t>
+          <t>NVIDIA RTX 5914</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -3440,12 +3440,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MacBook Air 93</t>
+          <t>HP Gen 4 CB-c012</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -3461,12 +3461,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>HP Gen 8 Jc-b515</t>
+          <t>MacBook Pro 97</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -3482,12 +3482,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MacBook Pro 32</t>
+          <t>Dell a769</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -3503,12 +3503,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 433</t>
+          <t>HP Gen 5 yo-k315</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -3524,12 +3524,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NVIDIA RTX 4277</t>
+          <t>Intel Core i7-002K</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -3545,12 +3545,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>NVIDIA GeForce 033</t>
+          <t>MacBook Air 94</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -3566,12 +3566,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Intel Core i5-653K</t>
+          <t>Intel Core i9-494K</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -3587,12 +3587,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>HP Gen 3 dq-U817</t>
+          <t>NVIDIA RTX 4429</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Elvia Beatriz</t>
+          <t>Aura Esperanza</t>
         </is>
       </c>
       <c r="C151" t="n">
